--- a/49915_Intercuenca_49915/_raw_reportes_xlsx/IDConfig_65217_completo.xlsx
+++ b/49915_Intercuenca_49915/_raw_reportes_xlsx/IDConfig_65217_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R385ae52333c44ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6d3a600ace324568"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,546 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.6180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49915_Intercuenca_49915/_raw_reportes_xlsx/IDConfig_65217_completo.xlsx
+++ b/49915_Intercuenca_49915/_raw_reportes_xlsx/IDConfig_65217_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6d3a600ace324568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdb907308d3dc428b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2826 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.6980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.9880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.8980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.8880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.8780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.8680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.8880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.8980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.4080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.5880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.6680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.7780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.8680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.0980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.1780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.5680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.2180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
